--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:13:57+00:00</t>
+    <t>2023-06-15T09:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Organization.meta.extension:as-data-trace</t>
-  </si>
-  <si>
-    <t>as-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t>Organization.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:14:52+00:00</t>
+    <t>2023-06-16T14:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1302,6 +1302,10 @@
     <t>Human contact for the organization.</t>
   </si>
   <si>
+    <t xml:space="preserve">profile:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1
 org-3</t>
   </si>
@@ -1431,22 +1435,17 @@
     <t>ContactPoint.period</t>
   </si>
   <si>
-    <t>Organization.telecom.period.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>Organization.telecom.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
+    <t>Organization.telecom:mailbox-mss</t>
+  </si>
+  <si>
+    <t>mailbox-mss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+</t>
+  </si>
+  <si>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -1575,13 +1574,13 @@
 </t>
   </si>
   <si>
-    <t>Point de contact.</t>
+    <t>Contact for the organization for a certain purpose</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
   </si>
   <si>
-    <t>Personne ou service agissant comme point de contact auprès d'une autre personne ou d'un autre service.</t>
+    <t>Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
@@ -1653,306 +1652,11 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:code}
-</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss</t>
-  </si>
-  <si>
-    <t>mailbox-mss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
-</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>AS Mailbox Metadata</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Type de boîte aux lettres.</t>
-  </si>
-  <si>
-    <t>Synonyme : typeBAL 
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Type de  boîte aux lettre MSS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
-  </si>
-  <si>
-    <t>Description fonctionnelle de la boîte aux lettres.</t>
-  </si>
-  <si>
-    <t>Synonyme : description</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
-  </si>
-  <si>
-    <t>responsible</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
-  </si>
-  <si>
-    <t>service</t>
-  </si>
-  <si>
-    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
-  </si>
-  <si>
-    <t>Synonyme : serviceRattachement</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
-  </si>
-  <si>
-    <t>digitization</t>
-  </si>
-  <si>
-    <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »). - O : Dématérialisation acceptée 
-- N : Dématérialisation refusée.</t>
-  </si>
-  <si>
-    <t>Synonyme : dematerialisation</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication</t>
-  </si>
-  <si>
-    <t>publication</t>
-  </si>
-  <si>
-    <t>Indicateur liste rouge. O: Boîte aux lettres en liste rouge;
-N: La boîte aux lettres peut être publiée</t>
-  </si>
-  <si>
-    <t>Synonyme : listeRouge</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.value</t>
-  </si>
-  <si>
-    <t>BAL MSS</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.use</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.rank</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom:mailbox-mss.period</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom.period</t>
   </si>
   <si>
     <t>Organization.contact.address</t>
@@ -2296,11 +2000,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ162"/>
+  <dimension ref="A1:AJ110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="104.8828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.87890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.0078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="35.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -2308,7 +2012,7 @@
     <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="143.859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2325,7 +2029,7 @@
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="108.3828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -10930,16 +10634,14 @@
         <v>35</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>403</v>
@@ -10951,18 +10653,18 @@
         <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11059,10 +10761,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11161,13 +10863,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="C87" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>61</v>
@@ -11189,10 +10891,10 @@
         <v>35</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>153</v>
@@ -11265,10 +10967,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11294,13 +10996,13 @@
         <v>123</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11329,10 +11031,10 @@
         <v>228</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>35</v>
@@ -11350,7 +11052,7 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -11359,7 +11061,7 @@
         <v>42</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>81</v>
@@ -11367,10 +11069,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11396,16 +11098,16 @@
         <v>56</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
@@ -11454,7 +11156,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11471,10 +11173,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11500,16 +11202,16 @@
         <v>123</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>35</v>
@@ -11537,10 +11239,10 @@
         <v>228</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>35</v>
@@ -11558,7 +11260,7 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
@@ -11575,10 +11277,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11601,16 +11303,16 @@
         <v>43</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11660,7 +11362,7 @@
         <v>35</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
@@ -11677,10 +11379,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11691,7 +11393,7 @@
         <v>36</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>35</v>
@@ -11706,13 +11408,13 @@
         <v>175</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11762,7 +11464,7 @@
         <v>35</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -11779,12 +11481,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D93" t="s" s="2">
         <v>35</v>
       </c>
@@ -11796,7 +11500,7 @@
         <v>36</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>35</v>
@@ -11805,16 +11509,20 @@
         <v>35</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>56</v>
+        <v>453</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>57</v>
+        <v>454</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>35</v>
       </c>
@@ -11862,31 +11570,31 @@
         <v>35</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>59</v>
+        <v>403</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>35</v>
+        <v>411</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11896,7 +11604,7 @@
         <v>37</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>35</v>
@@ -11905,18 +11613,20 @@
         <v>35</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>62</v>
+        <v>456</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>63</v>
+        <v>457</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>64</v>
+        <v>458</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
       </c>
@@ -11952,19 +11662,19 @@
         <v>35</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>69</v>
+        <v>455</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11976,15 +11686,15 @@
         <v>54</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>70</v>
+        <v>461</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11995,7 +11705,7 @@
         <v>36</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>35</v>
@@ -12007,18 +11717,20 @@
         <v>43</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>185</v>
+        <v>463</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>187</v>
+        <v>465</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>35</v>
       </c>
@@ -12066,7 +11778,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>189</v>
+        <v>462</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -12075,18 +11787,18 @@
         <v>42</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>190</v>
+        <v>54</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12106,27 +11818,23 @@
         <v>35</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>455</v>
+        <v>57</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q96" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
         <v>35</v>
       </c>
@@ -12170,7 +11878,7 @@
         <v>35</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
@@ -12179,22 +11887,22 @@
         <v>42</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12204,7 +11912,7 @@
         <v>37</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>35</v>
@@ -12213,20 +11921,18 @@
         <v>35</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>457</v>
+        <v>62</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>458</v>
+        <v>63</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>459</v>
+        <v>64</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>35</v>
       </c>
@@ -12262,19 +11968,19 @@
         <v>35</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>456</v>
+        <v>69</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
@@ -12286,15 +11992,15 @@
         <v>54</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>462</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12317,20 +12023,18 @@
         <v>43</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>464</v>
+        <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>35</v>
       </c>
@@ -12378,7 +12082,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12387,18 +12091,18 @@
         <v>42</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>54</v>
+        <v>475</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12418,18 +12122,20 @@
         <v>35</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>57</v>
+        <v>477</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>35</v>
@@ -12454,13 +12160,13 @@
         <v>35</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>35</v>
+        <v>480</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>35</v>
+        <v>287</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>35</v>
@@ -12478,7 +12184,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>59</v>
+        <v>481</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12487,29 +12193,29 @@
         <v>42</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>35</v>
@@ -12518,19 +12224,19 @@
         <v>35</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>62</v>
+        <v>215</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>63</v>
+        <v>483</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>64</v>
+        <v>484</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>65</v>
+        <v>485</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12568,39 +12274,39 @@
         <v>35</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>69</v>
+        <v>486</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12626,13 +12332,13 @@
         <v>56</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12682,7 +12388,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12691,7 +12397,7 @@
         <v>42</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>476</v>
+        <v>54</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>81</v>
@@ -12699,10 +12405,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12713,7 +12419,7 @@
         <v>36</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>35</v>
@@ -12722,21 +12428,23 @@
         <v>35</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>89</v>
+        <v>493</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
       </c>
@@ -12760,13 +12468,13 @@
         <v>35</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>481</v>
+        <v>35</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>287</v>
+        <v>35</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>35</v>
@@ -12784,13 +12492,13 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>54</v>
@@ -12801,10 +12509,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12824,20 +12532,18 @@
         <v>35</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>484</v>
+        <v>57</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>35</v>
@@ -12886,7 +12592,7 @@
         <v>35</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>487</v>
+        <v>59</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>36</v>
@@ -12895,29 +12601,29 @@
         <v>42</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>35</v>
@@ -12926,19 +12632,19 @@
         <v>35</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>489</v>
+        <v>63</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>490</v>
+        <v>64</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>491</v>
+        <v>65</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12976,74 +12682,74 @@
         <v>35</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>492</v>
+        <v>69</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>35</v>
+        <v>501</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H105" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I105" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="J105" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>494</v>
+        <v>62</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>498</v>
+        <v>212</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>35</v>
@@ -13092,7 +12798,7 @@
         <v>35</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -13104,15 +12810,15 @@
         <v>54</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13135,16 +12841,20 @@
         <v>35</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>57</v>
+        <v>506</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
       </c>
@@ -13168,13 +12878,13 @@
         <v>35</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>35</v>
+        <v>510</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>35</v>
+        <v>511</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>35</v>
@@ -13192,7 +12902,7 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>59</v>
+        <v>505</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -13201,29 +12911,29 @@
         <v>42</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>35</v>
@@ -13235,18 +12945,20 @@
         <v>35</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>62</v>
+        <v>513</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>63</v>
+        <v>514</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>64</v>
+        <v>515</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>35</v>
       </c>
@@ -13282,43 +12994,43 @@
         <v>35</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>69</v>
+        <v>512</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>502</v>
+        <v>35</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13331,25 +13043,23 @@
         <v>35</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>62</v>
+        <v>404</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>503</v>
+        <v>454</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>212</v>
+        <v>519</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>35</v>
@@ -13398,7 +13108,7 @@
         <v>35</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13410,15 +13120,15 @@
         <v>54</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>70</v>
+        <v>520</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13441,19 +13151,19 @@
         <v>35</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>233</v>
+        <v>522</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>508</v>
+        <v>458</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
@@ -13478,13 +13188,13 @@
         <v>35</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>511</v>
+        <v>35</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>512</v>
+        <v>35</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>35</v>
@@ -13502,7 +13212,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13519,10 +13229,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13533,10 +13243,10 @@
         <v>36</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>35</v>
@@ -13545,19 +13255,19 @@
         <v>35</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>35</v>
@@ -13606,5299 +13316,23 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AC111" s="2"/>
-      <c r="AD111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="D115" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="D116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="D119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="D124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="D129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="D134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="D139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="D144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O144" s="2"/>
-      <c r="P144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="146" hidden="true">
-      <c r="A146" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-      <c r="P146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="147" hidden="true">
-      <c r="A147" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E147" s="2"/>
-      <c r="F147" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G147" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O147" s="2"/>
-      <c r="P147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q147" s="2"/>
-      <c r="R147" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
-      <c r="P148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="D149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O149" s="2"/>
-      <c r="P149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
-      <c r="P150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O152" s="2"/>
-      <c r="P152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="P157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O159" s="2"/>
-      <c r="P159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O160" s="2"/>
-      <c r="P160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ162">
+  <autoFilter ref="A1:AJ110">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18908,7 +13342,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI161">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-16T14:16:48+00:00</t>
+    <t>2023-07-03T12:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T12:37:47+00:00</t>
+    <t>2023-07-10T14:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:48:30+00:00</t>
+    <t>2023-07-10T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,7 +665,7 @@
 </t>
   </si>
   <si>
-    <t>Numéro de la licence d'exploitation d’une officine.</t>
+    <t>Numéro de la licence d'exploitation d’une officine (Synonyme : numeroLicence).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
@@ -930,9 +930,6 @@
 Entité Géographique : GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
-    <t>typeStructure</t>
-  </si>
-  <si>
     <t>http://interopsante.org/fhir/ValueSet/fr-organization-type</t>
   </si>
   <si>
@@ -1213,10 +1210,7 @@
   </si>
   <si>
     <t>Toute entité juridique et chacun de ses établissements (EG) se voit attribuer par l'Insee, lors de son inscription au répertoire SIRENE, un code caractérisant son activité principale par référence à la nomenclature d'activités française (NAF rév. 2).
-Plus précisément, on distingue le code APET pour les EG.</t>
-  </si>
-  <si>
-    <t>Synonyme : codeAPEN</t>
+Plus précisément, on distingue le code APET pour les EG (Synonyme : codeAPEN).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
@@ -1228,10 +1222,7 @@
     <t>statutJuridiqueINSEE</t>
   </si>
   <si>
-    <t>Statut juridique FINESS qui caractérise la situation juridique de la personne morale.</t>
-  </si>
-  <si>
-    <t>Synonyme : statutJuridiqueINSEE</t>
+    <t>Statut juridique FINESS qui caractérise la situation juridique de la personne morale (Synonyme : statutJuridiqueINSEE).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
@@ -1243,10 +1234,7 @@
     <t>sphParticipation</t>
   </si>
   <si>
-    <t>Modalités de participation au service public hospitalier.</t>
-  </si>
-  <si>
-    <t>Synonyme : modaliteParticipationSPH</t>
+    <t>Modalités de participation au service public hospitalier (Synonyme : modaliteParticipationSPH).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J162-ESPIC-RASS/FHIR/JDV-J162-ESPIC-RASS</t>
@@ -1255,13 +1243,13 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Raison sociale de la structure.</t>
+    <t>Raison sociale de la structure (Synonyme : raisonSociale, dénomination).</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
   </si>
   <si>
-    <t>Synonyme : raisonSociale, dénomination</t>
+    <t>If the name of an organization changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
     <t>Need to use the name as the label of the organization.</t>
@@ -1270,13 +1258,13 @@
     <t>Organization.alias</t>
   </si>
   <si>
-    <t>Enseigne commerciale de la structure.</t>
+    <t>Enseigne commerciale de la structure (Synonyme : complementRaisonSociale).</t>
   </si>
   <si>
     <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
   </si>
   <si>
-    <t>Synonyme : complementRaisonSociale</t>
+    <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the organization.</t>
   </si>
   <si>
     <t>Over time locations and organizations go through many changes and can be known by different names.
@@ -1461,7 +1449,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>adresse</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
@@ -1667,9 +1655,6 @@
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
@@ -6368,7 +6353,7 @@
         <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>279</v>
@@ -6402,7 +6387,7 @@
         <v>280</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>35</v>
@@ -6437,10 +6422,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6537,10 +6522,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6639,10 +6624,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6668,16 +6653,16 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>35</v>
@@ -6726,7 +6711,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6743,10 +6728,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6843,10 +6828,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6945,10 +6930,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6974,65 +6959,65 @@
         <v>89</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7049,10 +7034,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7078,13 +7063,13 @@
         <v>56</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7134,7 +7119,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7151,10 +7136,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7180,16 +7165,16 @@
         <v>123</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>35</v>
@@ -7238,7 +7223,7 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7255,10 +7240,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7284,16 +7269,16 @@
         <v>56</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>35</v>
@@ -7342,7 +7327,7 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7359,10 +7344,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7388,16 +7373,16 @@
         <v>269</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>35</v>
@@ -7446,7 +7431,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7463,10 +7448,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7492,16 +7477,16 @@
         <v>56</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7550,7 +7535,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7567,13 +7552,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>35</v>
@@ -7635,10 +7620,10 @@
         <v>228</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>35</v>
@@ -7673,10 +7658,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7773,10 +7758,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7875,10 +7860,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7904,16 +7889,16 @@
         <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>35</v>
@@ -7962,7 +7947,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -7979,10 +7964,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8079,10 +8064,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8181,10 +8166,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8210,29 +8195,29 @@
         <v>89</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N61" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>35</v>
@@ -8268,7 +8253,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -8285,10 +8270,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8314,13 +8299,13 @@
         <v>56</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8370,7 +8355,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8387,10 +8372,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8416,16 +8401,16 @@
         <v>123</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
@@ -8474,7 +8459,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8491,10 +8476,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8520,16 +8505,16 @@
         <v>56</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>35</v>
@@ -8578,7 +8563,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -8595,10 +8580,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8624,16 +8609,16 @@
         <v>269</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>35</v>
@@ -8682,7 +8667,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -8699,10 +8684,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8728,16 +8713,16 @@
         <v>56</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>35</v>
@@ -8786,7 +8771,7 @@
         <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -8803,13 +8788,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>35</v>
@@ -8871,10 +8856,10 @@
         <v>228</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>35</v>
@@ -8909,10 +8894,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9009,10 +8994,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9111,10 +9096,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9140,16 +9125,16 @@
         <v>101</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>35</v>
@@ -9198,7 +9183,7 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -9215,10 +9200,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9315,10 +9300,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9417,10 +9402,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9446,23 +9431,23 @@
         <v>89</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N73" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>35</v>
@@ -9504,7 +9489,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9521,10 +9506,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9550,13 +9535,13 @@
         <v>56</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9606,7 +9591,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -9623,10 +9608,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9652,16 +9637,16 @@
         <v>123</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>35</v>
@@ -9710,7 +9695,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -9727,10 +9712,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9756,16 +9741,16 @@
         <v>56</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>35</v>
@@ -9814,7 +9799,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -9831,10 +9816,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9860,16 +9845,16 @@
         <v>269</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>35</v>
@@ -9918,7 +9903,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -9935,10 +9920,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9964,16 +9949,16 @@
         <v>56</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>35</v>
@@ -10022,7 +10007,7 @@
         <v>35</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -10039,13 +10024,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>35</v>
@@ -10070,13 +10055,13 @@
         <v>233</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>277</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>279</v>
@@ -10108,7 +10093,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>35</v>
@@ -10143,13 +10128,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>35</v>
@@ -10174,13 +10159,13 @@
         <v>233</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>277</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>386</v>
+        <v>278</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>279</v>
@@ -10212,7 +10197,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>35</v>
@@ -10247,13 +10232,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>35</v>
@@ -10278,13 +10263,13 @@
         <v>233</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>277</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>391</v>
+        <v>278</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>279</v>
@@ -10316,7 +10301,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>35</v>
@@ -10351,10 +10336,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10380,16 +10365,16 @@
         <v>56</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>35</v>
@@ -10438,7 +10423,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -10455,10 +10440,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10484,16 +10469,16 @@
         <v>56</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>35</v>
@@ -10542,7 +10527,7 @@
         <v>35</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
@@ -10559,10 +10544,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10585,19 +10570,19 @@
         <v>35</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>35</v>
@@ -10634,7 +10619,7 @@
         <v>35</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -10644,7 +10629,7 @@
         <v>68</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
@@ -10653,18 +10638,18 @@
         <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10761,10 +10746,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10863,13 +10848,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>61</v>
@@ -10891,10 +10876,10 @@
         <v>35</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>153</v>
@@ -10967,10 +10952,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10996,13 +10981,13 @@
         <v>123</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11031,10 +11016,10 @@
         <v>228</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>35</v>
@@ -11052,7 +11037,7 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -11061,7 +11046,7 @@
         <v>42</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>81</v>
@@ -11069,10 +11054,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11098,16 +11083,16 @@
         <v>56</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
@@ -11156,7 +11141,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11173,10 +11158,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11202,16 +11187,16 @@
         <v>123</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>35</v>
@@ -11239,10 +11224,10 @@
         <v>228</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>35</v>
@@ -11260,7 +11245,7 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
@@ -11277,10 +11262,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11303,16 +11288,16 @@
         <v>43</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11362,7 +11347,7 @@
         <v>35</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
@@ -11379,10 +11364,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11408,13 +11393,13 @@
         <v>175</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11464,7 +11449,7 @@
         <v>35</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -11481,13 +11466,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>35</v>
@@ -11509,19 +11494,19 @@
         <v>35</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>35</v>
@@ -11570,7 +11555,7 @@
         <v>35</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11582,15 +11567,15 @@
         <v>54</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11613,19 +11598,19 @@
         <v>35</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
@@ -11674,7 +11659,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11686,15 +11671,15 @@
         <v>54</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11717,19 +11702,19 @@
         <v>43</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>35</v>
@@ -11778,7 +11763,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -11795,10 +11780,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11895,10 +11880,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11997,10 +11982,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12026,13 +12011,13 @@
         <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12082,7 +12067,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12091,7 +12076,7 @@
         <v>42</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>81</v>
@@ -12099,10 +12084,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12128,13 +12113,13 @@
         <v>89</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12163,10 +12148,10 @@
         <v>105</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>35</v>
@@ -12184,7 +12169,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12201,10 +12186,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12230,13 +12215,13 @@
         <v>215</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12286,7 +12271,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12303,10 +12288,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12332,13 +12317,13 @@
         <v>56</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12388,7 +12373,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12405,10 +12390,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12431,19 +12416,19 @@
         <v>35</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12492,7 +12477,7 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
@@ -12509,10 +12494,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12609,10 +12594,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12711,14 +12696,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -12740,10 +12725,10 @@
         <v>62</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>65</v>
@@ -12798,7 +12783,7 @@
         <v>35</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -12815,10 +12800,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12844,16 +12829,16 @@
         <v>233</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
@@ -12881,10 +12866,10 @@
         <v>105</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>35</v>
@@ -12902,7 +12887,7 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -12919,10 +12904,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12945,19 +12930,19 @@
         <v>35</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>35</v>
@@ -13006,7 +12991,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13023,10 +13008,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13049,17 +13034,17 @@
         <v>35</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>35</v>
@@ -13108,7 +13093,7 @@
         <v>35</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13120,15 +13105,15 @@
         <v>54</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13151,19 +13136,19 @@
         <v>35</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>524</v>
+        <v>455</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
@@ -13212,7 +13197,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13229,10 +13214,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13255,19 +13240,19 @@
         <v>35</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>35</v>
@@ -13316,7 +13301,7 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$146</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4755" uniqueCount="579">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:51:06+00:00</t>
+    <t>2023-07-11T12:08:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -697,13 +697,20 @@
 </t>
   </si>
   <si>
-    <t>Une instance par identifiant (FINESS, SIREN, SIRET, idNat_Struct…).</t>
+    <t>Identifies this organization  across multiple systems</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
   </si>
   <si>
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:system}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the identifier.system pattern</t>
   </si>
   <si>
     <t>ele-1
@@ -731,9 +738,6 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>official</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -753,26 +757,135 @@
 </t>
   </si>
   <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-organization-identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt</t>
+  </si>
+  <si>
+    <t>idNatSt</t>
+  </si>
+  <si>
+    <t>Identifiant idNat_Struct qui doit correspondre à l'idnat struct tel que défini dans l'Annexe Transverse – Source des données métier pour les professionnels et les structures : https://esante.gouv.fr/sites/default/files/media_entity/documents/ci-sis_anx_sources-donnees-professionnels-structures_v1.5_0.pdf</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.use</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.type</t>
+  </si>
+  <si>
     <t>Les codes FINEJ, FINEG, SIREN, SIRET, IDNST, INTRN proviennent de la terminologie  http://interopsante.org/CodeSystem/fr-v2-0203 
  Les codes 0,4 proviennent de la terminologie TRE-G07-TypeIdentifiantStructure.</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-organization-identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -784,90 +897,130 @@
 En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J104-TypeIdentifiantStructure-RASS peut être utilisé. {f:type}</t>
   </si>
   <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>« urn:oid:1.2.250.1.71.4.2.2 » si l’instance correspond à l’identification nationale des structures (idNat_Struct)
- « http://sirene.fr» si l’instance correspond à un identifiant SIREN ou SIRET 
- « http://finess.sante.gouv.fr» si l’instance correspond à un identifiant FINESS EG ou EJ 
- « urn:oid:1.2.250.1.213.1.6.4.3 » si l’instance correspond à un identifiant ADELI rang ou RPPS rang
-« https://annuaire.sante.fr » si l’instance correspond à l’identifiant technique de la structure.</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>Identification nationale de la structure, Numéro SIRET, Numéro SIREN, Numéro FINESS Etablissement, Numéro FINESS EJ, RPPS rang, ADELI rang, Identifiant technique de la structure.</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+    <t>Organization.identifier:idNatSt.system</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.71.4.2.2</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.value</t>
+  </si>
+  <si>
+    <t>Identification nationale de la structure préfixé : 3 + Numéro SIRET, 2 + Numéro SIREN, 1 + Numéro FINESS Etablissement, 1 + Numéro FINESS EJ, 4 + RPPS rang, 0 + ADELI rang, Identifiant technique de la structure.</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:idNatSt.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene</t>
+  </si>
+  <si>
+    <t>sirene</t>
+  </si>
+  <si>
+    <t>Identifiant SIREN ou SIRET</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.system</t>
+  </si>
+  <si>
+    <t>http://sirene.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess</t>
+  </si>
+  <si>
+    <t>finess</t>
+  </si>
+  <si>
+    <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.system</t>
+  </si>
+  <si>
+    <t>http://finess.sante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps</t>
+  </si>
+  <si>
+    <t>adeliRpps</t>
+  </si>
+  <si>
+    <t>Identifiant ADELI rang ou RPPS rang</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.system</t>
+  </si>
+  <si>
+    <t>https://annuaire.sante.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.assigner</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1985,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ110"/>
+  <dimension ref="A1:AJ146"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
@@ -5259,16 +5412,16 @@
         <v>35</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>214</v>
@@ -5280,7 +5433,7 @@
         <v>37</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -5288,10 +5441,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5388,10 +5541,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5490,10 +5643,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5519,23 +5672,23 @@
         <v>123</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>227</v>
+        <v>35</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>35</v>
@@ -5553,13 +5706,13 @@
         <v>35</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>35</v>
@@ -5577,7 +5730,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5594,10 +5747,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5620,19 +5773,19 @@
         <v>43</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>35</v>
@@ -5660,10 +5813,10 @@
         <v>105</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>35</v>
@@ -5681,7 +5834,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5693,7 +5846,7 @@
         <v>54</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6111,49 +6264,47 @@
         <v>268</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q41" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
         <v>35</v>
       </c>
@@ -6197,16 +6348,16 @@
         <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>81</v>
@@ -6214,10 +6365,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6228,32 +6379,28 @@
         <v>36</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>57</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>35</v>
       </c>
@@ -6277,62 +6424,62 @@
         <v>35</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>280</v>
+        <v>35</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>281</v>
+        <v>35</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>35</v>
@@ -6341,23 +6488,21 @@
         <v>35</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>285</v>
+        <v>63</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>35</v>
       </c>
@@ -6381,31 +6526,31 @@
         <v>35</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>280</v>
+        <v>35</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>286</v>
+        <v>35</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>275</v>
+        <v>69</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6417,15 +6562,15 @@
         <v>54</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6442,22 +6587,26 @@
         <v>35</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
       </c>
@@ -6466,7 +6615,7 @@
         <v>35</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>35</v>
+        <v>274</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>35</v>
@@ -6481,13 +6630,13 @@
         <v>35</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>35</v>
@@ -6505,7 +6654,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6514,29 +6663,29 @@
         <v>42</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>35</v>
@@ -6545,21 +6694,23 @@
         <v>35</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>63</v>
+        <v>276</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
       </c>
@@ -6583,51 +6734,51 @@
         <v>35</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>70</v>
+        <v>277</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6650,19 +6801,19 @@
         <v>43</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>243</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>244</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>296</v>
+        <v>246</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>35</v>
@@ -6672,10 +6823,10 @@
         <v>35</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>35</v>
+        <v>247</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>35</v>
@@ -6711,13 +6862,13 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>54</v>
@@ -6728,10 +6879,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
+        <v>249</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6739,7 +6890,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>42</v>
@@ -6751,18 +6902,20 @@
         <v>35</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>57</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>35</v>
@@ -6775,7 +6928,7 @@
         <v>35</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>35</v>
@@ -6811,7 +6964,7 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -6820,29 +6973,29 @@
         <v>42</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>35</v>
@@ -6851,19 +7004,19 @@
         <v>35</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>65</v>
+        <v>258</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6901,39 +7054,39 @@
         <v>35</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>69</v>
+        <v>259</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>70</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6941,10 +7094,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>35</v>
@@ -6956,32 +7109,30 @@
         <v>43</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>35</v>
@@ -7017,7 +7168,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7029,17 +7180,19 @@
         <v>54</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>35</v>
       </c>
@@ -7048,7 +7201,7 @@
         <v>36</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>35</v>
@@ -7060,18 +7213,18 @@
         <v>43</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>35</v>
       </c>
@@ -7119,16 +7272,16 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>315</v>
+        <v>214</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>81</v>
@@ -7136,10 +7289,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7159,23 +7312,19 @@
         <v>35</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>57</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>35</v>
       </c>
@@ -7223,7 +7372,7 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7232,29 +7381,29 @@
         <v>42</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>324</v>
+        <v>223</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>35</v>
@@ -7263,23 +7412,21 @@
         <v>35</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>325</v>
+        <v>63</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>35</v>
       </c>
@@ -7315,39 +7462,39 @@
         <v>35</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>69</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>224</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7364,25 +7511,25 @@
         <v>35</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>269</v>
+        <v>123</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>225</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>226</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>334</v>
+        <v>228</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>35</v>
@@ -7407,13 +7554,13 @@
         <v>35</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>35</v>
@@ -7431,7 +7578,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7448,10 +7595,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7459,7 +7606,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>42</v>
@@ -7474,19 +7621,19 @@
         <v>43</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>235</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>339</v>
+        <v>236</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>340</v>
+        <v>237</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>341</v>
+        <v>238</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7511,13 +7658,13 @@
         <v>35</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>35</v>
@@ -7535,7 +7682,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7552,20 +7699,18 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>42</v>
@@ -7580,19 +7725,19 @@
         <v>43</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -7602,10 +7747,10 @@
         <v>35</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>35</v>
+        <v>292</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>35</v>
+        <v>247</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>35</v>
@@ -7617,13 +7762,13 @@
         <v>35</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>345</v>
+        <v>35</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>346</v>
+        <v>35</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>35</v>
@@ -7641,13 +7786,13 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>54</v>
@@ -7658,10 +7803,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7669,7 +7814,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>42</v>
@@ -7681,18 +7826,20 @@
         <v>35</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>57</v>
+        <v>250</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -7705,7 +7852,7 @@
         <v>35</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>35</v>
@@ -7741,7 +7888,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -7750,29 +7897,29 @@
         <v>42</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>35</v>
@@ -7781,19 +7928,19 @@
         <v>35</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>65</v>
+        <v>258</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7831,39 +7978,39 @@
         <v>35</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>69</v>
+        <v>259</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>70</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>349</v>
+        <v>295</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7871,10 +8018,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>35</v>
@@ -7886,20 +8033,18 @@
         <v>43</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>35</v>
       </c>
@@ -7947,29 +8092,31 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>350</v>
+        <v>296</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>35</v>
       </c>
@@ -7978,7 +8125,7 @@
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>35</v>
@@ -7987,19 +8134,21 @@
         <v>35</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>57</v>
+        <v>298</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>35</v>
       </c>
@@ -8047,38 +8196,38 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>35</v>
@@ -8090,17 +8239,15 @@
         <v>35</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>35</v>
@@ -8137,50 +8284,50 @@
         <v>35</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>303</v>
+        <v>223</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>35</v>
@@ -8189,35 +8336,33 @@
         <v>35</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>353</v>
+        <v>63</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>353</v>
+        <v>64</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>35</v>
@@ -8241,39 +8386,39 @@
         <v>35</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>309</v>
+        <v>69</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>355</v>
+        <v>301</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>311</v>
+        <v>224</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8290,24 +8435,26 @@
         <v>35</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>312</v>
+        <v>225</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>35</v>
       </c>
@@ -8331,13 +8478,13 @@
         <v>35</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>35</v>
@@ -8355,7 +8502,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8372,10 +8519,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>317</v>
+        <v>233</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8383,7 +8530,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>42</v>
@@ -8398,19 +8545,19 @@
         <v>43</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>318</v>
+        <v>235</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
@@ -8435,13 +8582,13 @@
         <v>35</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>35</v>
@@ -8459,7 +8606,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>322</v>
+        <v>241</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8476,10 +8623,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>357</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8487,7 +8634,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>42</v>
@@ -8502,19 +8649,19 @@
         <v>43</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>35</v>
@@ -8524,10 +8671,10 @@
         <v>35</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>35</v>
+        <v>304</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>35</v>
+        <v>247</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>35</v>
@@ -8563,7 +8710,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>328</v>
+        <v>248</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -8580,10 +8727,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>330</v>
+        <v>249</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8591,7 +8738,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>42</v>
@@ -8606,20 +8753,18 @@
         <v>43</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>269</v>
+        <v>56</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>331</v>
+        <v>250</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>35</v>
       </c>
@@ -8631,7 +8776,7 @@
         <v>35</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>35</v>
@@ -8667,7 +8812,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -8684,10 +8829,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8698,7 +8843,7 @@
         <v>36</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>35</v>
@@ -8710,20 +8855,18 @@
         <v>43</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>35</v>
       </c>
@@ -8771,7 +8914,7 @@
         <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>342</v>
+        <v>259</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -8783,19 +8926,17 @@
         <v>54</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>307</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>35</v>
       </c>
@@ -8804,7 +8945,7 @@
         <v>36</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>35</v>
@@ -8816,20 +8957,18 @@
         <v>43</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>35</v>
       </c>
@@ -8853,13 +8992,13 @@
         <v>35</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>363</v>
+        <v>35</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>35</v>
@@ -8877,29 +9016,31 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>35</v>
       </c>
@@ -8908,7 +9049,7 @@
         <v>36</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>35</v>
@@ -8917,19 +9058,21 @@
         <v>35</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>57</v>
+        <v>310</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>35</v>
       </c>
@@ -8977,38 +9120,38 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>365</v>
+        <v>311</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>35</v>
@@ -9020,17 +9163,15 @@
         <v>35</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>35</v>
@@ -9067,50 +9208,50 @@
         <v>35</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>35</v>
@@ -9119,23 +9260,21 @@
         <v>35</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>293</v>
+        <v>63</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>294</v>
+        <v>64</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>35</v>
       </c>
@@ -9171,19 +9310,19 @@
         <v>35</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>297</v>
+        <v>69</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -9195,15 +9334,15 @@
         <v>54</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>367</v>
+        <v>313</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>299</v>
+        <v>224</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9220,22 +9359,26 @@
         <v>35</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>35</v>
       </c>
@@ -9259,13 +9402,13 @@
         <v>35</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>35</v>
@@ -9283,7 +9426,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9292,29 +9435,29 @@
         <v>42</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>368</v>
+        <v>314</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>301</v>
+        <v>233</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>35</v>
@@ -9323,21 +9466,23 @@
         <v>35</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>63</v>
+        <v>235</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>35</v>
       </c>
@@ -9361,51 +9506,51 @@
         <v>35</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9431,29 +9576,29 @@
         <v>89</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>370</v>
+        <v>243</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>370</v>
+        <v>244</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>371</v>
+        <v>35</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>35</v>
+        <v>247</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>35</v>
@@ -9489,7 +9634,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9506,10 +9651,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>372</v>
+        <v>317</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9517,7 +9662,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>42</v>
@@ -9535,13 +9680,13 @@
         <v>56</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9555,7 +9700,7 @@
         <v>35</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>35</v>
@@ -9591,7 +9736,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -9608,10 +9753,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>317</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9622,7 +9767,7 @@
         <v>36</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>35</v>
@@ -9634,20 +9779,18 @@
         <v>43</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>35</v>
       </c>
@@ -9695,7 +9838,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -9707,15 +9850,15 @@
         <v>54</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>374</v>
+        <v>319</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>324</v>
+        <v>261</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9726,7 +9869,7 @@
         <v>36</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>35</v>
@@ -9738,20 +9881,18 @@
         <v>43</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>35</v>
       </c>
@@ -9799,7 +9940,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>328</v>
+        <v>266</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -9811,15 +9952,15 @@
         <v>54</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9827,39 +9968,41 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>42</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="R77" t="s" s="2">
         <v>35</v>
       </c>
@@ -9903,7 +10046,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -9920,10 +10063,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9934,10 +10077,10 @@
         <v>36</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>35</v>
@@ -9946,19 +10089,19 @@
         <v>43</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>35</v>
@@ -9983,37 +10126,35 @@
         <v>35</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>35</v>
+        <v>332</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>35</v>
+        <v>333</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>54</v>
@@ -10024,13 +10165,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>35</v>
@@ -10040,7 +10181,7 @@
         <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>35</v>
@@ -10052,19 +10193,19 @@
         <v>43</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>35</v>
@@ -10089,11 +10230,13 @@
         <v>35</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>35</v>
@@ -10111,7 +10254,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -10128,14 +10271,12 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>35</v>
       </c>
@@ -10144,7 +10285,7 @@
         <v>36</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>35</v>
@@ -10153,23 +10294,19 @@
         <v>35</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>383</v>
+        <v>57</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>35</v>
       </c>
@@ -10193,11 +10330,13 @@
         <v>35</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>384</v>
+        <v>35</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>35</v>
@@ -10215,33 +10354,31 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10257,23 +10394,21 @@
         <v>35</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>387</v>
+        <v>63</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>35</v>
       </c>
@@ -10297,29 +10432,31 @@
         <v>35</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>388</v>
+        <v>35</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>275</v>
+        <v>69</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -10331,15 +10468,15 @@
         <v>54</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>389</v>
+        <v>343</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10347,13 +10484,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>42</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>35</v>
@@ -10362,19 +10499,19 @@
         <v>43</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>35</v>
@@ -10423,16 +10560,16 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>81</v>
@@ -10440,10 +10577,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10454,10 +10591,10 @@
         <v>36</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>35</v>
@@ -10469,17 +10606,13 @@
         <v>56</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>395</v>
+        <v>57</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>35</v>
       </c>
@@ -10527,31 +10660,31 @@
         <v>35</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>394</v>
+        <v>59</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>399</v>
+        <v>353</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10561,7 +10694,7 @@
         <v>37</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>35</v>
@@ -10570,20 +10703,18 @@
         <v>35</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>400</v>
+        <v>62</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>401</v>
+        <v>63</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>402</v>
+        <v>64</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>35</v>
       </c>
@@ -10619,9 +10750,11 @@
         <v>35</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AC84" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>67</v>
+      </c>
       <c r="AD84" t="s" s="2">
         <v>35</v>
       </c>
@@ -10629,7 +10762,7 @@
         <v>68</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
@@ -10638,18 +10771,18 @@
         <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>406</v>
+        <v>54</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>407</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>408</v>
+        <v>355</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10657,7 +10790,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>42</v>
@@ -10669,31 +10802,35 @@
         <v>35</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>35</v>
+        <v>360</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>35</v>
+        <v>360</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>35</v>
@@ -10729,7 +10866,7 @@
         <v>35</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>59</v>
+        <v>361</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
@@ -10738,29 +10875,29 @@
         <v>42</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>35</v>
@@ -10769,19 +10906,19 @@
         <v>35</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>63</v>
+        <v>364</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>64</v>
+        <v>365</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>65</v>
+        <v>366</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10819,45 +10956,43 @@
         <v>35</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>69</v>
+        <v>367</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10873,21 +11008,23 @@
         <v>35</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>412</v>
+        <v>123</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>153</v>
+        <v>371</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>35</v>
       </c>
@@ -10935,27 +11072,27 @@
         <v>35</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>69</v>
+        <v>374</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10963,7 +11100,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>42</v>
@@ -10978,18 +11115,20 @@
         <v>43</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>416</v>
+        <v>378</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>35</v>
       </c>
@@ -11013,13 +11152,13 @@
         <v>35</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>418</v>
+        <v>35</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>419</v>
+        <v>35</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>35</v>
@@ -11037,7 +11176,7 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -11046,7 +11185,7 @@
         <v>42</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>421</v>
+        <v>54</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>81</v>
@@ -11054,10 +11193,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>422</v>
+        <v>381</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11065,7 +11204,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>42</v>
@@ -11080,19 +11219,19 @@
         <v>43</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>56</v>
+        <v>321</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>424</v>
+        <v>384</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
@@ -11141,7 +11280,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11158,10 +11297,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11178,25 +11317,25 @@
         <v>35</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>35</v>
@@ -11221,13 +11360,13 @@
         <v>35</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>433</v>
+        <v>35</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>434</v>
+        <v>35</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>35</v>
@@ -11245,7 +11384,7 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
@@ -11262,12 +11401,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>35</v>
       </c>
@@ -11288,18 +11429,20 @@
         <v>43</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>437</v>
+        <v>234</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>439</v>
+        <v>329</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>35</v>
       </c>
@@ -11323,13 +11466,13 @@
         <v>35</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>35</v>
+        <v>397</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>35</v>
+        <v>398</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>35</v>
@@ -11347,13 +11490,13 @@
         <v>35</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>327</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>54</v>
@@ -11364,10 +11507,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>442</v>
+        <v>399</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11378,7 +11521,7 @@
         <v>36</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>35</v>
@@ -11387,20 +11530,18 @@
         <v>35</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>443</v>
+        <v>57</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>35</v>
@@ -11449,7 +11590,7 @@
         <v>35</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>446</v>
+        <v>59</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -11458,34 +11599,32 @@
         <v>42</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>260</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>35</v>
@@ -11494,20 +11633,18 @@
         <v>35</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>449</v>
+        <v>62</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>450</v>
+        <v>63</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>402</v>
+        <v>64</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>35</v>
       </c>
@@ -11543,19 +11680,19 @@
         <v>35</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11567,15 +11704,15 @@
         <v>54</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>407</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>451</v>
+        <v>401</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
+        <v>344</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11583,34 +11720,34 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I94" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K94" t="s" s="2">
-        <v>452</v>
+        <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>453</v>
+        <v>345</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>454</v>
+        <v>346</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>455</v>
+        <v>347</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>456</v>
+        <v>348</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
@@ -11659,7 +11796,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>451</v>
+        <v>349</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11671,15 +11808,15 @@
         <v>54</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>457</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>458</v>
+        <v>402</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>458</v>
+        <v>351</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11699,23 +11836,19 @@
         <v>35</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>459</v>
+        <v>56</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>35</v>
       </c>
@@ -11763,7 +11896,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>458</v>
+        <v>59</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -11772,29 +11905,29 @@
         <v>42</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>267</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>464</v>
+        <v>403</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>464</v>
+        <v>353</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>35</v>
@@ -11806,15 +11939,17 @@
         <v>35</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>65</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>35</v>
@@ -11851,50 +11986,50 @@
         <v>35</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>465</v>
+        <v>355</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>35</v>
@@ -11903,33 +12038,35 @@
         <v>35</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>63</v>
+        <v>405</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>64</v>
+        <v>405</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>35</v>
+        <v>406</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>35</v>
+        <v>406</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>35</v>
@@ -11953,39 +12090,39 @@
         <v>35</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>69</v>
+        <v>361</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>466</v>
+        <v>363</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12011,13 +12148,13 @@
         <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>467</v>
+        <v>364</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>468</v>
+        <v>365</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>469</v>
+        <v>366</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12067,7 +12204,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>470</v>
+        <v>367</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12076,7 +12213,7 @@
         <v>42</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>471</v>
+        <v>54</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>81</v>
@@ -12084,10 +12221,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>472</v>
+        <v>408</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>472</v>
+        <v>369</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12110,18 +12247,20 @@
         <v>43</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>473</v>
+        <v>370</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>474</v>
+        <v>371</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>35</v>
       </c>
@@ -12145,13 +12284,13 @@
         <v>35</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>476</v>
+        <v>35</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>286</v>
+        <v>35</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>35</v>
@@ -12169,7 +12308,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>477</v>
+        <v>374</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12186,10 +12325,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>409</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>478</v>
+        <v>376</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12212,18 +12351,20 @@
         <v>43</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>479</v>
+        <v>377</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>480</v>
+        <v>378</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>35</v>
       </c>
@@ -12271,7 +12412,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>482</v>
+        <v>380</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12288,10 +12429,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>483</v>
+        <v>382</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12314,18 +12455,20 @@
         <v>43</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>56</v>
+        <v>321</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>484</v>
+        <v>383</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>485</v>
+        <v>384</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>35</v>
       </c>
@@ -12373,7 +12516,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>487</v>
+        <v>387</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12390,10 +12533,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>488</v>
+        <v>411</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>488</v>
+        <v>389</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12404,7 +12547,7 @@
         <v>36</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>35</v>
@@ -12413,22 +12556,22 @@
         <v>35</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>489</v>
+        <v>56</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>490</v>
+        <v>390</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>491</v>
+        <v>391</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>492</v>
+        <v>392</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>493</v>
+        <v>393</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12477,13 +12620,13 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>488</v>
+        <v>394</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>54</v>
@@ -12494,12 +12637,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>494</v>
+        <v>412</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="D103" t="s" s="2">
         <v>35</v>
       </c>
@@ -12517,19 +12662,23 @@
         <v>35</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>35</v>
       </c>
@@ -12553,13 +12702,13 @@
         <v>35</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>35</v>
+        <v>414</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>35</v>
+        <v>415</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>35</v>
@@ -12577,38 +12726,38 @@
         <v>35</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>59</v>
+        <v>327</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>495</v>
+        <v>416</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>495</v>
+        <v>340</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>35</v>
@@ -12620,17 +12769,15 @@
         <v>35</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>35</v>
@@ -12667,43 +12814,43 @@
         <v>35</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>496</v>
+        <v>417</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>496</v>
+        <v>342</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>497</v>
+        <v>61</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -12716,26 +12863,24 @@
         <v>35</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>62</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>498</v>
+        <v>63</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>499</v>
+        <v>64</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>35</v>
       </c>
@@ -12771,19 +12916,19 @@
         <v>35</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>500</v>
+        <v>69</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -12800,10 +12945,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>501</v>
+        <v>418</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>501</v>
+        <v>344</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12811,7 +12956,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>42</v>
@@ -12823,22 +12968,22 @@
         <v>35</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>502</v>
+        <v>345</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>503</v>
+        <v>346</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>504</v>
+        <v>347</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>505</v>
+        <v>348</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
@@ -12863,13 +13008,13 @@
         <v>35</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>506</v>
+        <v>35</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>507</v>
+        <v>35</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>35</v>
@@ -12887,13 +13032,13 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>501</v>
+        <v>349</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>54</v>
@@ -12904,10 +13049,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>508</v>
+        <v>419</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>508</v>
+        <v>351</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12930,20 +13075,16 @@
         <v>35</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>509</v>
+        <v>56</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>510</v>
+        <v>57</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>35</v>
       </c>
@@ -12991,7 +13132,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>508</v>
+        <v>59</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13000,22 +13141,22 @@
         <v>42</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>514</v>
+        <v>420</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>514</v>
+        <v>353</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13034,18 +13175,18 @@
         <v>35</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>400</v>
+        <v>62</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>450</v>
+        <v>63</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>35</v>
       </c>
@@ -13081,19 +13222,19 @@
         <v>35</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>514</v>
+        <v>69</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13105,15 +13246,15 @@
         <v>54</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>516</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>517</v>
+        <v>421</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>517</v>
+        <v>355</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13121,7 +13262,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>42</v>
@@ -13133,29 +13274,29 @@
         <v>35</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>518</v>
+        <v>89</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>519</v>
+        <v>422</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>455</v>
+        <v>358</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>520</v>
+        <v>359</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>35</v>
+        <v>423</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>35</v>
@@ -13197,7 +13338,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>517</v>
+        <v>361</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13214,10 +13355,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>424</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>363</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13228,32 +13369,30 @@
         <v>36</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H110" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J110" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I110" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K110" t="s" s="2">
-        <v>522</v>
+        <v>56</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>523</v>
+        <v>364</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>524</v>
+        <v>365</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>35</v>
       </c>
@@ -13301,23 +13440,3733 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>367</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y115" s="2"/>
+      <c r="Z115" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y116" s="2"/>
+      <c r="Z116" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y117" s="2"/>
+      <c r="Z117" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AC120" s="2"/>
+      <c r="AD120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ110">
+  <autoFilter ref="A1:AJ146">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13327,7 +17176,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI109">
+  <conditionalFormatting sqref="A2:AI145">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7761" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7761" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1490,13 +1490,14 @@
     <t>Organization.active</t>
   </si>
   <si>
-    <t>La ressource est-elle active? (active | inactive)</t>
+    <t>La ressource est-elle active? (active | inactive). true par défaut; false pour les structures supprimées.</t>
   </si>
   <si>
     <t>Whether the organization's record is still in active use.</t>
   </si>
   <si>
-    <t>true par défaut; false pour les structures supprimées.</t>
+    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
   </si>
   <si>
     <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
@@ -1854,9 +1855,6 @@
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>https://www.hl7.org/fhir/valueset-contact-point-system.html</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -2233,13 +2231,13 @@
 </t>
   </si>
   <si>
-    <t>Référence vers la structure de rattachement (lien EG/ EJ).</t>
+    <t>Référence vers la structure de rattachement (lien EG/ EJ). Chaque entité geographique et ratachée à une entité juridique. C'est l'id de la ressource de l'entité juridique à laquelle est ratachée la structure qui est remontée dans l'element de référence partOf de l'entité géographique.</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
   </si>
   <si>
-    <t>Chaque entité geographique et ratachée à une entité juridique. C'est l'id de la ressource de l'entité juridique à laquelle est ratachée la structure qui est remontée dans l'element de référence partOf de l'entité géographique.</t>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>Need to be able to track the hierarchy of organizations within an organization.</t>
@@ -2438,9 +2436,6 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the organization.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>Organizations have multiple systems that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
@@ -20189,7 +20184,7 @@
         <v>589</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>590</v>
+        <v>379</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20218,37 +20213,37 @@
         <v>285</v>
       </c>
       <c r="Y170" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z170" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z170" t="s" s="2">
+      <c r="AA170" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF170" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AA170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF170" t="s" s="2">
+      <c r="AG170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI170" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>94</v>
@@ -20256,10 +20251,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20285,16 +20280,16 @@
         <v>96</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N171" t="s" s="2">
+      <c r="O171" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>73</v>
@@ -20343,7 +20338,7 @@
         <v>73</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>74</v>
@@ -20360,10 +20355,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20389,16 +20384,16 @@
         <v>162</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>73</v>
@@ -20426,28 +20421,28 @@
         <v>285</v>
       </c>
       <c r="Y172" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z172" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="Z172" t="s" s="2">
+      <c r="AA172" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF172" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD172" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>74</v>
@@ -20464,10 +20459,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20490,16 +20485,16 @@
         <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L173" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="M173" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -20549,7 +20544,7 @@
         <v>73</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>74</v>
@@ -20566,10 +20561,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20595,10 +20590,10 @@
         <v>212</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>314</v>
@@ -20651,7 +20646,7 @@
         <v>73</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>74</v>
@@ -20668,13 +20663,13 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>572</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>73</v>
@@ -20696,10 +20691,10 @@
         <v>73</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="M175" t="s" s="2">
         <v>575</v>
@@ -20774,7 +20769,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>581</v>
@@ -20874,7 +20869,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>582</v>
@@ -20976,7 +20971,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>582</v>
@@ -21078,13 +21073,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>582</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>73</v>
@@ -21106,13 +21101,13 @@
         <v>73</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -21180,10 +21175,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21280,10 +21275,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B181" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21382,13 +21377,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C182" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>73</v>
@@ -21413,10 +21408,10 @@
         <v>102</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -21484,10 +21479,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21584,10 +21579,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B184" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21613,10 +21608,10 @@
         <v>102</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -21684,10 +21679,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21727,7 +21722,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>73</v>
@@ -21786,10 +21781,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21849,7 +21844,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>73</v>
@@ -21884,10 +21879,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>193</v>
@@ -21915,10 +21910,10 @@
         <v>102</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -21986,10 +21981,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -22086,10 +22081,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -22115,10 +22110,10 @@
         <v>102</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -22186,10 +22181,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -22288,10 +22283,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -22388,13 +22383,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C192" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>73</v>
@@ -22419,10 +22414,10 @@
         <v>102</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -22490,10 +22485,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22590,10 +22585,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22619,10 +22614,10 @@
         <v>102</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -22690,10 +22685,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22733,7 +22728,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>73</v>
@@ -22792,10 +22787,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22892,13 +22887,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>73</v>
@@ -22923,10 +22918,10 @@
         <v>102</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -22994,10 +22989,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -23094,10 +23089,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -23123,10 +23118,10 @@
         <v>102</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -23194,10 +23189,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -23237,7 +23232,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>73</v>
@@ -23296,10 +23291,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -23396,13 +23391,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>73</v>
@@ -23427,10 +23422,10 @@
         <v>102</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -23498,10 +23493,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -23598,10 +23593,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23627,10 +23622,10 @@
         <v>102</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -23698,10 +23693,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -23741,7 +23736,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>73</v>
@@ -23800,10 +23795,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23900,13 +23895,13 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C207" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>73</v>
@@ -23931,10 +23926,10 @@
         <v>102</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -24002,10 +23997,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -24102,10 +24097,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -24131,10 +24126,10 @@
         <v>102</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -24202,10 +24197,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -24245,7 +24240,7 @@
       </c>
       <c r="Q210" s="2"/>
       <c r="R210" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="S210" t="s" s="2">
         <v>73</v>
@@ -24304,10 +24299,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -24404,13 +24399,13 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C212" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="D212" t="s" s="2">
         <v>73</v>
@@ -24435,10 +24430,10 @@
         <v>102</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -24506,10 +24501,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24606,10 +24601,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24635,10 +24630,10 @@
         <v>102</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -24706,10 +24701,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24749,7 +24744,7 @@
       </c>
       <c r="Q215" s="2"/>
       <c r="R215" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="S215" t="s" s="2">
         <v>73</v>
@@ -24808,10 +24803,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24908,10 +24903,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B217" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24951,7 +24946,7 @@
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="S217" t="s" s="2">
         <v>73</v>
@@ -25010,10 +25005,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B218" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -25036,7 +25031,7 @@
         <v>73</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>213</v>
@@ -25110,7 +25105,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>587</v>
@@ -25156,7 +25151,7 @@
         <v>73</v>
       </c>
       <c r="S219" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="T219" t="s" s="2">
         <v>73</v>
@@ -25174,37 +25169,37 @@
         <v>285</v>
       </c>
       <c r="Y219" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z219" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z219" t="s" s="2">
+      <c r="AA219" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF219" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AA219" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB219" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC219" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD219" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE219" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF219" t="s" s="2">
+      <c r="AG219" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI219" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AG219" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH219" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI219" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>94</v>
@@ -25212,10 +25207,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25241,16 +25236,16 @@
         <v>96</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="M220" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N220" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N220" t="s" s="2">
+      <c r="O220" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="O220" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>73</v>
@@ -25299,7 +25294,7 @@
         <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
@@ -25316,10 +25311,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25345,16 +25340,16 @@
         <v>162</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M221" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M221" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="N221" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>73</v>
@@ -25382,28 +25377,28 @@
         <v>285</v>
       </c>
       <c r="Y221" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z221" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="Z221" t="s" s="2">
+      <c r="AA221" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF221" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AA221" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB221" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC221" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD221" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE221" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF221" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
@@ -25420,10 +25415,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25446,16 +25441,16 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L222" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L222" t="s" s="2">
+      <c r="M222" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M222" t="s" s="2">
+      <c r="N222" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
@@ -25505,7 +25500,7 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
@@ -25522,10 +25517,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25551,10 +25546,10 @@
         <v>212</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="N223" t="s" s="2">
         <v>314</v>
@@ -25607,7 +25602,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25624,10 +25619,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25650,19 +25645,19 @@
         <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="L224" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="L224" t="s" s="2">
+      <c r="M224" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="M224" t="s" s="2">
+      <c r="N224" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="N224" t="s" s="2">
+      <c r="O224" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="O224" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>73</v>
@@ -25711,7 +25706,7 @@
         <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
@@ -25723,15 +25718,15 @@
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25754,19 +25749,19 @@
         <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="L225" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="L225" t="s" s="2">
+      <c r="M225" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="M225" t="s" s="2">
+      <c r="N225" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="N225" t="s" s="2">
+      <c r="O225" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>73</v>
@@ -25815,7 +25810,7 @@
         <v>73</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>74</v>
@@ -25832,10 +25827,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25932,10 +25927,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -26034,10 +26029,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -26063,13 +26058,13 @@
         <v>96</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M228" t="s" s="2">
+      <c r="N228" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -26119,16 +26114,16 @@
         <v>73</v>
       </c>
       <c r="AF228" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG228" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH228" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI228" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AJ228" t="s" s="2">
         <v>94</v>
@@ -26136,10 +26131,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26165,13 +26160,13 @@
         <v>128</v>
       </c>
       <c r="L229" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M229" t="s" s="2">
+      <c r="N229" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
@@ -26200,7 +26195,7 @@
         <v>144</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Z229" t="s" s="2">
         <v>488</v>
@@ -26221,7 +26216,7 @@
         <v>73</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>74</v>
@@ -26238,10 +26233,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26267,13 +26262,13 @@
         <v>271</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="M230" t="s" s="2">
+      <c r="N230" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -26323,7 +26318,7 @@
         <v>73</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>74</v>
@@ -26340,10 +26335,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -26369,13 +26364,13 @@
         <v>96</v>
       </c>
       <c r="L231" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M231" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="M231" t="s" s="2">
+      <c r="N231" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
@@ -26425,7 +26420,7 @@
         <v>73</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>74</v>
@@ -26442,10 +26437,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -26468,19 +26463,19 @@
         <v>73</v>
       </c>
       <c r="K232" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="L232" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="L232" t="s" s="2">
+      <c r="M232" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="M232" t="s" s="2">
+      <c r="N232" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="N232" t="s" s="2">
+      <c r="O232" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>73</v>
@@ -26529,7 +26524,7 @@
         <v>73</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>74</v>
@@ -26546,10 +26541,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26646,10 +26641,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26748,14 +26743,14 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
@@ -26777,10 +26772,10 @@
         <v>102</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="M235" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="N235" t="s" s="2">
         <v>105</v>
@@ -26835,7 +26830,7 @@
         <v>73</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>74</v>
@@ -26852,10 +26847,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26881,16 +26876,16 @@
         <v>290</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M236" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="M236" t="s" s="2">
+      <c r="N236" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="N236" t="s" s="2">
+      <c r="O236" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>73</v>
@@ -26918,11 +26913,11 @@
         <v>144</v>
       </c>
       <c r="Y236" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="Z236" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="Z236" t="s" s="2">
-        <v>758</v>
-      </c>
       <c r="AA236" t="s" s="2">
         <v>73</v>
       </c>
@@ -26939,7 +26934,7 @@
         <v>73</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>74</v>
@@ -26956,10 +26951,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26982,19 +26977,19 @@
         <v>73</v>
       </c>
       <c r="K237" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="L237" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="L237" t="s" s="2">
+      <c r="M237" t="s" s="2">
         <v>761</v>
       </c>
-      <c r="M237" t="s" s="2">
+      <c r="N237" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="N237" t="s" s="2">
+      <c r="O237" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>73</v>
@@ -27043,7 +27038,7 @@
         <v>73</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>74</v>
@@ -27060,10 +27055,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -27089,14 +27084,14 @@
         <v>573</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M238" t="s" s="2">
         <v>575</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>73</v>
@@ -27145,7 +27140,7 @@
         <v>73</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>74</v>
@@ -27157,15 +27152,15 @@
         <v>93</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -27188,19 +27183,19 @@
         <v>73</v>
       </c>
       <c r="K239" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="L239" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="L239" t="s" s="2">
+      <c r="M239" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N239" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="O239" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="O239" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>73</v>
@@ -27249,7 +27244,7 @@
         <v>73</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>74</v>
@@ -27266,10 +27261,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -27292,19 +27287,19 @@
         <v>73</v>
       </c>
       <c r="K240" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L240" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="L240" t="s" s="2">
+      <c r="M240" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M240" t="s" s="2">
+      <c r="N240" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="O240" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O240" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>73</v>
@@ -27353,7 +27348,7 @@
         <v>73</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>74</v>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7761" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7762" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -20980,7 +20980,7 @@
         <v>584</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -21007,7 +21007,9 @@
       <c r="M178" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N178" s="2"/>
+      <c r="N178" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>73</v>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/main/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
